--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97551</v>
+        <v>97553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97553</v>
+        <v>97646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77412</v>
+        <v>77447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97646</v>
+        <v>97658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77447</v>
+        <v>77451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97658</v>
+        <v>97660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77451</v>
+        <v>77453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97660</v>
+        <v>97661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97661</v>
+        <v>97688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77453</v>
+        <v>77480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97688</v>
+        <v>97701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77480</v>
+        <v>77482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77482</v>
+        <v>77486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
         <v>128390138</v>
       </c>
       <c r="B10" t="n">
-        <v>97705</v>
+        <v>97712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128390071</v>
       </c>
       <c r="B11" t="n">
-        <v>77486</v>
+        <v>77427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,12 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>104015</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436273.4710950674</v>
+        <v>436273</v>
       </c>
       <c r="R6" t="n">
-        <v>6196001.630579057</v>
+        <v>6196002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,19 +1284,9 @@
           <t>1995-08-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1995-08-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106776</v>
+        <v>106779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106779</v>
+        <v>106805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106805</v>
+        <v>106806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106806</v>
+        <v>106807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106807</v>
+        <v>106809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106809</v>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106813</v>
+        <v>106826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>640113</v>
+        <v>487767</v>
       </c>
       <c r="B2" t="n">
-        <v>93144</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>1116</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436344.6454373571</v>
+        <v>436353</v>
       </c>
       <c r="R2" t="n">
-        <v>6195990.492906435</v>
+        <v>6195990</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-01-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-01-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lönn, ask</t>
+          <t>riklig på ved av levande bok</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,12 +767,17 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter</t>
+          <t>1 substratenheter # bok</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,37 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>725288</v>
+        <v>352993</v>
       </c>
       <c r="B3" t="n">
-        <v>93141</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>1342</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -858,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436344.6454373571</v>
+        <v>436345</v>
       </c>
       <c r="R3" t="n">
-        <v>6195990.492906435</v>
+        <v>6195990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,24 +872,14 @@
           <t>2009-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lönn</t>
+          <t>Bok</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,12 +917,7 @@
         <v>352994</v>
       </c>
       <c r="B4" t="n">
-        <v>75909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436232.1608037455</v>
+        <v>436232</v>
       </c>
       <c r="R4" t="n">
-        <v>6196019.05536199</v>
+        <v>6196019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,19 +991,9 @@
           <t>2009-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1077,15 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>352993</v>
+        <v>128390071</v>
       </c>
       <c r="B5" t="n">
-        <v>75909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,26 +1061,20 @@
           <t>(Weigel) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Maltesholm, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436344.6454373571</v>
+        <v>436339</v>
       </c>
       <c r="R5" t="n">
-        <v>6195990.492906435</v>
+        <v>6195956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,27 +1101,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-09-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bok</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,26 +1115,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Dahlberg</t>
+          <t>Hans Ingvarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Dahlberg</t>
+          <t>Hans Ingvarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1214,7 +1137,7 @@
         <v>494658</v>
       </c>
       <c r="B6" t="n">
-        <v>106826</v>
+        <v>107042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,43 +1250,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>487767</v>
+        <v>640113</v>
       </c>
       <c r="B7" t="n">
-        <v>73544</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1372,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436352.5078125156</v>
+        <v>436345</v>
       </c>
       <c r="R7" t="n">
-        <v>6195990.377199465</v>
+        <v>6195990</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,27 +1324,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-01-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-01-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>riklig på ved av levande bok</t>
+          <t>Lönn, ask</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,17 +1346,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # bok</t>
+          <t>2 substratenheter</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,37 +1369,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97369573</v>
+        <v>725288</v>
       </c>
       <c r="B8" t="n">
-        <v>60166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101258</v>
+        <v>2668</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bukspolsnäcka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Macrogastra ventricosa</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Draparnaud, 1801)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1500,24 +1402,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Maltesholm, provyta 25, Sk</t>
+          <t>Maltesholm, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436335.7347768974</v>
+        <v>436345</v>
       </c>
       <c r="R8" t="n">
-        <v>6195957.552496199</v>
+        <v>6195990</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1541,27 +1443,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1982-09-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1982-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Inventering på uppdrag av länsstyrelsen (Jfr rapport Gärdenfors 2021)</t>
+          <t>Lönn</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,67 +1465,65 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Torr bokskog med enstaka askar. Inget buskskikt. Frodigt fältskikt där skogsbingel (Mercuralis perennis) starkt dominerar, men även gott om brännässla och hallon. Sållning av tunn och torr bokförna, samt mot kanten av kärrdrog</t>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Johan Dahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Johan Dahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97369512</v>
+        <v>97369573</v>
       </c>
       <c r="B9" t="n">
-        <v>60230</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61525</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101526</v>
+        <v>101258</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tandsnäcka</t>
+          <t>Bukspolsnäcka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perforatella bidentata</t>
+          <t>Macrogastra ventricosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gmelin, 1788)</t>
+          <t>(Draparnaud, 1801)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>sållning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1642,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436335.7347768974</v>
+        <v>436336</v>
       </c>
       <c r="R9" t="n">
-        <v>6195957.552496199</v>
+        <v>6195958</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1675,19 +1565,9 @@
           <t>1982-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1982-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1724,52 +1604,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128390138</v>
+        <v>97369512</v>
       </c>
       <c r="B10" t="n">
-        <v>97712</v>
+        <v>61589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220250</v>
+        <v>101526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tandsnäcka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Perforatella bidentata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gmelin, 1788)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>sållning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maltesholm, Sk</t>
+          <t>Maltesholm, provyta 25, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436290</v>
+        <v>436336</v>
       </c>
       <c r="R10" t="n">
-        <v>6195990</v>
+        <v>6195958</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1793,12 +1678,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>1982-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>1982-09-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av länsstyrelsen (Jfr rapport Gärdenfors 2021)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,56 +1697,61 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Torr bokskog med enstaka askar. Inget buskskikt. Frodigt fältskikt där skogsbingel (Mercuralis perennis) starkt dominerar, men även gott om brännässla och hallon. Sållning av tunn och torr bokförna, samt mot kanten av kärrdrog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128390071</v>
+        <v>128390138</v>
       </c>
       <c r="B11" t="n">
-        <v>77427</v>
+        <v>98186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1342</v>
+        <v>220250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1864,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436339</v>
+        <v>436290</v>
       </c>
       <c r="R11" t="n">
-        <v>6195956</v>
+        <v>6195990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43497-2025 artfynd.xlsx
+++ b/artfynd/A 43497-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/352994</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/494658</t>
         </is>
       </c>
     </row>
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128390138</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/487767</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/352993</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128390071</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/640113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/725288</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97369573</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1819,8 +1869,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97369512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>